--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_phrase_translation_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_phrase_translation_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток?</t>
+          <t>Qué является the location of Эйбенсток?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,29 +509,31 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток? Answer: The place of the es the is in the sentence. The es the is a preposition. The es the is a pre</t>
+          <t>Qué является the location of Эйбенсток? Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Answer: The place of the es the is in the sentence. The es the is a preposition. The es the is a pre</t>
+          <t>Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' place', 1.0), (' of', 1.0), (' the', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' sentence', 1.0), ('.', 1.0), (' The', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0), ('position', 1.0), ('.', 1.0), (' The', 0.5), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0)]</t>
+          <t>[(' Э', 1.0), ('й', 1.0), ('б', 1.0), ('ен', 1.0), ('ст', 1.0), ('ок', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' population', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -544,7 +546,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток?</t>
+          <t>Qué является the location of Эйбенсток?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,29 +559,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток? Answer: The place of the es the is in the sentence. The es the is a preposition. It is used to show the</t>
+          <t>Qué является the location of Эйбенсток? Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Answer: The place of the es the is in the sentence. The es the is a preposition. It is used to show the</t>
+          <t>Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' place', 1.0), (' of', 1.0), (' the', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' sentence', 1.0), ('.', 1.0), (' The', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0), ('position', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' used', 1.0), (' to', 1.0), (' show', 1.0), (' the', 1.0)]</t>
+          <t>[(' Э', 1.0), ('й', 1.0), ('б', 1.0), ('ен', 1.0), ('ст', 1.0), ('ок', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' population', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -592,7 +596,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток?</t>
+          <t>Qué является the location of Эйбенсток?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -605,29 +609,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток? Answer: The place of the es the is in the sentence. The es the is a preposition. The es the is a pre</t>
+          <t>Qué является the location of Эйбенсток? Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Answer: The place of the es the is in the sentence. The es the is a preposition. The es the is a pre</t>
+          <t>Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' place', 1.0), (' of', 1.0), (' the', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' sentence', 1.0), ('.', 1.0), (' The', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0), ('position', 1.0), ('.', 1.0), (' The', 0.5), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0)]</t>
+          <t>[(' Э', 1.0), ('й', 1.0), ('б', 1.0), ('ен', 1.0), ('ст', 1.0), ('ок', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' population', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -640,7 +646,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток?</t>
+          <t>Qué является the location of Эйбенсток?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -653,29 +659,31 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток? Answer: The place of the es the is in the sentence. The es the is a preposition. It is used to show the</t>
+          <t>Qué является the location of Эйбенсток? Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Answer: The place of the es the is in the sentence. The es the is a preposition. It is used to show the</t>
+          <t>Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' place', 1.0), (' of', 1.0), (' the', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' sentence', 1.0), ('.', 1.0), (' The', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0), ('position', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' used', 1.0), (' to', 1.0), (' show', 1.0), (' the', 1.0)]</t>
+          <t>[(' Э', 1.0), ('й', 1.0), ('б', 1.0), ('ен', 1.0), ('ст', 1.0), ('ок', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' population', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -688,7 +696,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток?</t>
+          <t>Qué является the location of Эйбенсток?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -701,29 +709,31 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>What es the の場所 Эйбенсток? Answer: The place of the es the is in the sentence. The es the is a preposition. It is used to show the</t>
+          <t>Qué является the location of Эйбенсток? Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Answer: The place of the es the is in the sentence. The es the is a preposition. It is used to show the</t>
+          <t>Answer: Эйбенсток is located in the state of New York, United States of America.
+What is the population of</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9726549386978149</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' place', 1.0), (' of', 1.0), (' the', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' sentence', 1.0), ('.', 1.0), (' The', 1.0), (' es', 1.0), (' the', 1.0), (' is', 1.0), (' a', 1.0), (' pre', 1.0), ('position', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' used', 1.0), (' to', 1.0), (' show', 1.0), (' the', 1.0)]</t>
+          <t>[(' Э', 1.0), ('й', 1.0), ('б', 1.0), ('ен', 1.0), ('ст', 1.0), ('ок', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' population', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -736,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа?</t>
+          <t>Что такое the の場所 Simcoe 複合 School?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -749,33 +759,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа? Answer: Simcoe Composite Школа is located in Simcoe, Ontario.://www.google.com/url?q=https://www</t>
+          <t>Что такое the の場所 Simcoe 複合 School? Answer: Simcoe County District School Board (SCDSB) is a public school board in Ontario, Canada. It is the largest</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite Школа is located in Simcoe, Ontario.://www.google.com/url?q=https://www</t>
+          <t>Answer: Simcoe County District School Board (SCDSB) is a public school board in Ontario, Canada</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.333299994468689</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9570032358169556</v>
+        <v>0.9659363031387329</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3662008047103882</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3333), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('www', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' County', 1.0), (' District', 1.0), (' School', 1.0), (' Board', 1.0), (' (', 1.0), ('SC', 1.0), ('DS', 1.0), ('B', 1.0), (')', 1.0), (' is', 1.0), (' a', 1.0), (' public', 1.0), (' school', 1.0), (' board', 1.0), (' in', 1.0), (' Ontario', 0.5), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -784,7 +794,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа?</t>
+          <t>Что такое the の場所 Simcoe 複合 School?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -797,33 +807,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа? Answer: Simcoe Composite Школа is located in Simcoe, Ontario.://www.google.com/url?q=https://www</t>
+          <t>Что такое the の場所 Simcoe 複合 School? Answer: Simcoe County District School Board (SCDSB) is a public school board in Ontario, Canada. It is the largest</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite Школа is located in Simcoe, Ontario.://www.google.com/url?q=https://www</t>
+          <t>Answer: Simcoe County District School Board (SCDSB) is a public school board in Ontario, Canada</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.333299994468689</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9570032358169556</v>
+        <v>0.9659363031387329</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3662008047103882</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3333), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('www', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' County', 1.0), (' District', 1.0), (' School', 1.0), (' Board', 1.0), (' (', 1.0), ('SC', 1.0), ('DS', 1.0), ('B', 1.0), (')', 1.0), (' is', 1.0), (' a', 1.0), (' public', 1.0), (' school', 1.0), (' board', 1.0), (' in', 1.0), (' Ontario', 0.5), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -832,7 +842,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа?</t>
+          <t>Что такое the の場所 Simcoe 複合 School?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -845,33 +855,33 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Che cosa est le location of Simcoe Composite Школа? Answer: Simcoe Composite Школа is located in Simcoe, Ontario. You can find Simcoe Composite Школа on </t>
+          <t>Что такое the の場所 Simcoe 複合 School? Answer: Simcoe County District School Board (SCDSB) is a public school board in Simcoe County, Ontario, Canada.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: Simcoe Composite Школа is located in Simcoe, Ontario. You can find Simcoe Composite Школа on </t>
+          <t>Answer: Simcoe County District School Board (SCDSB) is a public school board in Simcoe County, Ontario, Canada</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.333299994468689</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9570032358169556</v>
+        <v>0.9715319275856018</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3662008047103882</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' You', 0.3333), (' can', 1.0), (' find', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' on', 1.0), (' ', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' County', 1.0), (' District', 1.0), (' School', 1.0), (' Board', 1.0), (' (', 1.0), ('SC', 1.0), ('DS', 1.0), ('B', 1.0), (')', 1.0), (' is', 1.0), (' a', 1.0), (' public', 1.0), (' school', 1.0), (' board', 1.0), (' in', 1.0), (' Sim', 0.5), ('coe', 1.0), (' County', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -880,7 +890,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа?</t>
+          <t>Что такое the の場所 Simcoe 複合 School?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -893,33 +903,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Che cosa est le location of Simcoe Composite Школа? Answer: Simcoe Composite Школа is located in Simcoe, Ontario. You can find Simcoe Composite Школа on </t>
+          <t>Что такое the の場所 Simcoe 複合 School? Answer: Simcoe County District School Board (SCDSB) is a public school board in Ontario, Canada. It is the largest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer: Simcoe Composite Школа is located in Simcoe, Ontario. You can find Simcoe Composite Школа on </t>
+          <t>Answer: Simcoe County District School Board (SCDSB) is a public school board in Ontario, Canada</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.333299994468689</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9570032358169556</v>
+        <v>0.9659363031387329</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3662008047103882</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' You', 0.3333), (' can', 1.0), (' find', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' on', 1.0), (' ', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' County', 1.0), (' District', 1.0), (' School', 1.0), (' Board', 1.0), (' (', 1.0), ('SC', 1.0), ('DS', 1.0), ('B', 1.0), (')', 1.0), (' is', 1.0), (' a', 1.0), (' public', 1.0), (' school', 1.0), (' board', 1.0), (' in', 1.0), (' Ontario', 0.5), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -928,7 +938,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа?</t>
+          <t>Что такое the の場所 Simcoe 複合 School?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -941,33 +951,33 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Che cosa est le location of Simcoe Composite Школа? Answer: Simcoe Composite Школа is located in Simcoe, Ontario.://www.google.com/url?q=https://www</t>
+          <t>Что такое the の場所 Simcoe 複合 School? Answer: Simcoe County District School Board (SCDSB) is a public school board in Simcoe County, Ontario, Canada.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite Школа is located in Simcoe, Ontario.://www.google.com/url?q=https://www</t>
+          <t>Answer: Simcoe County District School Board (SCDSB) is a public school board in Simcoe County, Ontario, Canada</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.333299994468689</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9570032358169556</v>
+        <v>0.9715319275856018</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3662008047103882</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' Ш', 1.0), ('к', 1.0), ('ола', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3333), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('www', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' County', 1.0), (' District', 1.0), (' School', 1.0), (' Board', 1.0), (' (', 1.0), ('SC', 1.0), ('DS', 1.0), ('B', 1.0), (')', 1.0), (' is', 1.0), (' a', 1.0), (' public', 1.0), (' school', 1.0), (' board', 1.0), (' in', 1.0), (' Sim', 0.5), ('coe', 1.0), (' County', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +986,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность?</t>
+          <t>What Ist the location of Vrienden von der 田舎？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -989,33 +999,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность? Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>What Ist the location of Vrienden von der 田舎？ Answer: Vrienden van der Weide is located in the Netherlands. It is a small village in the province of Gelderland.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>Answer: Vrienden van der Weide is located in the Netherlands</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9438742995262146</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Friends', 1.0), (' is', 1.0), (' New', 0.6514), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' The', 1.0), (' show', 1.0), (' is', 1.0), (' set', 1.0), (' in', 1.0), (' New', 0.7773), (' York', 1.0), (' City', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), (' is', 1.0), (' filmed', 1.0), (' in', 1.0), (' Los', 1.0), (' Angeles', 1.0)]</t>
+          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' der', 1.0), (' We', 1.0), ('ide', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1024,7 +1034,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность?</t>
+          <t>What Ist the location of Vrienden von der 田舎？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1037,33 +1047,33 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность? Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>What Ist the location of Vrienden von der 田舎？ Answer: Vrienden van der Weide is located in the Netherlands. It is a small town in the province of Gelderland.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>Answer: Vrienden van der Weide is located in the Netherlands</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9438742995262146</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Friends', 1.0), (' is', 1.0), (' New', 0.6514), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' The', 1.0), (' show', 1.0), (' is', 1.0), (' set', 1.0), (' in', 1.0), (' New', 0.7773), (' York', 1.0), (' City', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), (' is', 1.0), (' filmed', 1.0), (' in', 1.0), (' Los', 1.0), (' Angeles', 1.0)]</t>
+          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' der', 1.0), (' We', 1.0), ('ide', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1072,7 +1082,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность?</t>
+          <t>What Ist the location of Vrienden von der 田舎？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1085,33 +1095,33 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность? Answer: The location of Friends is in New York City. The show is set in the fictional town of "Selmerville" in</t>
+          <t>What Ist the location of Vrienden von der 田舎？ Answer: Vrienden van der Weide is located in the Netherlands. It is a small town in the province of Gelderland.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Answer: The location of Friends is in New York City. The show is set in the fictional town of "Selmerville" in</t>
+          <t>Answer: Vrienden van der Weide is located in the Netherlands</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.1135390251874924</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9166547656059265</v>
+        <v>0.9438742995262146</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9931492805480957</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Friends', 1.0), (' is', 1.0), (' in', 0.3486), (' New', 1.0), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' The', 1.0), (' show', 1.0), (' is', 1.0), (' set', 1.0), (' in', 1.0), (' the', 0.5), (' fictional', 1.0), (' town', 1.0), (' of', 1.0), (' "', 1.0), ('S', 1.0), ('elm', 0.6514), ('erville', 1.0), ('"', 1.0), (' in', 1.0)]</t>
+          <t>[(' V', 0.5), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' der', 1.0), (' We', 1.0), ('ide', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1120,7 +1130,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность?</t>
+          <t>What Ist the location of Vrienden von der 田舎？</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1133,33 +1143,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность? Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>What Ist the location of Vrienden von der 田舎？ Answer: The location of Vrienden van der Hoeve is in the Netherlands. It is located in the city of Amsterdam. It</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>Answer: The location of Vrienden van der Hoeve is in the Netherlands</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Friends', 1.0), (' is', 1.0), (' New', 0.6514), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' The', 1.0), (' show', 1.0), (' is', 1.0), (' set', 1.0), (' in', 1.0), (' New', 0.7773), (' York', 1.0), (' City', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), (' is', 1.0), (' filmed', 1.0), (' in', 1.0), (' Los', 1.0), (' Angeles', 1.0)]</t>
+          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' der', 1.0), (' Hoe', 1.0), ('ve', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1168,7 +1178,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность?</t>
+          <t>What Ist the location of Vrienden von der 田舎？</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1181,33 +1191,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>What is the ubicación of Друзья Сельская местность? Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>What Ist the location of Vrienden von der 田舎？ Answer: The location of Vrienden van der Hoeve is in the Netherlands. It is located in the city of Amsterdam. The</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Answer: The location of Friends is New York City. The show is set in New York City, but it is filmed in Los Angeles</t>
+          <t>Answer: The location of Vrienden van der Hoeve is in the Netherlands</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9516951441764832</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' Friends', 1.0), (' is', 1.0), (' New', 0.6514), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' The', 1.0), (' show', 1.0), (' is', 1.0), (' set', 1.0), (' in', 1.0), (' New', 0.7773), (' York', 1.0), (' City', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), (' is', 1.0), (' filmed', 1.0), (' in', 1.0), (' Los', 1.0), (' Angeles', 1.0)]</t>
+          <t>[(' The', 0.5), (' location', 1.0), (' of', 1.0), (' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' der', 1.0), (' Hoe', 1.0), ('ve', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1216,7 +1226,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter?</t>
+          <t>What Ist Die emplacement de Cunter?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1229,29 +1239,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter? Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 48' 0" North, 9°</t>
+          <t>What Ist Die emplacement de Cunter? Answer: Cunter is located in the canton of Graubünden in Switzerland. It is situated in the district of Hinterrhe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 48' 0" North</t>
+          <t>Answer: Cunter is located in the canton of Graubünden in Switzerland</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.1252999901771545</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8782576322555542</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2602536976337433</v>
+        <v>-0</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Switzerland', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('46', 1.0), ('°', 1.0), (' ', 1.0), ('48', 0.1253)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' cant', 1.0), ('on', 1.0), (' of', 1.0), (' Gra', 1.0), ('ub', 1.0), ('ünden', 1.0), (' in', 1.0), (' Switzerland', 1.0)]</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1264,7 +1274,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter?</t>
+          <t>What Ist Die emplacement de Cunter?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1277,29 +1287,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter? Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 47' 0" North, 9°</t>
+          <t>What Ist Die emplacement de Cunter? Answer: Cunter is located in the canton of Graubünden in Switzerland. It is situated in the district of Hinterrhe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 47' 0" North</t>
+          <t>Answer: Cunter is located in the canton of Graubünden in Switzerland</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.4372999966144562</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9496175050735474</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3617064952850342</v>
+        <v>-0</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Switzerland', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('46', 1.0), ('°', 1.0), (' ', 1.0), ('47', 0.4373)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' cant', 1.0), ('on', 1.0), (' of', 1.0), (' Gra', 1.0), ('ub', 1.0), ('ünden', 1.0), (' in', 1.0), (' Switzerland', 1.0)]</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1312,7 +1322,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter?</t>
+          <t>What Ist Die emplacement de Cunter?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1325,29 +1335,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter? Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 46' 0" North, 9°</t>
+          <t>What Ist Die emplacement de Cunter? Answer: Cunter is located in the canton of Graubünden in Switzerland. It is situated in the district of Hinterrhe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 46' 0" North</t>
+          <t>Answer: Cunter is located in the canton of Graubünden in Switzerland</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.4372999966144562</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9496175050735474</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3617064952850342</v>
+        <v>-0</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Switzerland', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('46', 1.0), ('°', 1.0), (' ', 1.0), ('46', 0.4373)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' cant', 1.0), ('on', 1.0), (' of', 1.0), (' Gra', 1.0), ('ub', 1.0), ('ünden', 1.0), (' in', 1.0), (' Switzerland', 1.0)]</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1360,7 +1370,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter?</t>
+          <t>What Ist Die emplacement de Cunter?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1373,29 +1383,31 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter? Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 46' 0" North, 9°</t>
+          <t>What Ist Die emplacement de Cunter? Answer: Cunter is located in the canton of Graubünden in Switzerland.
+What Ist Die emplacement de Cunter?
+Answer</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 46' 0" North</t>
+          <t>Answer: Cunter is located in the canton of Graubünden in Switzerland</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.4372999966144562</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9496175050735474</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3617064952850342</v>
+        <v>-0</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Switzerland', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('46', 1.0), ('°', 1.0), (' ', 1.0), ('46', 0.4373)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' cant', 1.0), ('on', 1.0), (' of', 1.0), (' Gra', 1.0), ('ub', 1.0), ('ünden', 1.0), (' in', 1.0), (' Switzerland', 1.0)]</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1408,7 +1420,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter?</t>
+          <t>What Ist Die emplacement de Cunter?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1421,29 +1433,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>何 è il Posizione di Cunter? Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 46' 0" North, 9°</t>
+          <t>What Ist Die emplacement de Cunter? Answer: Cunter is located in the canton of Graubünden in Switzerland. It is situated in the district of Hinterrhe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in Switzerland and its geographical coordinates are 46° 46' 0" North</t>
+          <t>Answer: Cunter is located in the canton of Graubünden in Switzerland</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.4372999966144562</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9496175050735474</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3617064952850342</v>
+        <v>-0</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Switzerland', 1.0), (' and', 1.0), (' its', 1.0), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('46', 1.0), ('°', 1.0), (' ', 1.0), ('46', 0.4373)]</t>
+          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' cant', 1.0), ('on', 1.0), (' of', 1.0), (' Gra', 1.0), ('ub', 1.0), ('ünden', 1.0), (' in', 1.0), (' Switzerland', 1.0)]</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1456,7 +1468,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence?</t>
+          <t>What est l'emplacement of グレンクリー？</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1469,29 +1481,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence? Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t>What est l'emplacement of グレンクリー？ Answer: グレンクリー is located in the United States (USA) and the time zone America/New_York (UTC-5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t>Answer: グレンクリー is located in the United States (USA) and the time zone America/New_York (UTC-5</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I22" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('oe', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Ar', 1.0), ('gy', 1.0), ('ll', 1.0), (' and', 1.0), (' B', 1.0), ('ute', 1.0), (',', 1.0), (' Scotland', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' west', 1.0)]</t>
+          <t>[(' グ', 1.0), ('レン', 1.0), ('ク', 1.0), ('リー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' (', 1.0), ('USA', 1.0), (')', 1.0), (' and', 0.6514), (' the', 1.0), (' time', 1.0), (' zone', 1.0), (' America', 1.0), ('/New', 1.0), ('_Y', 1.0), ('ork', 1.0), (' (', 1.0), ('UTC', 1.0), ('-', 1.0), ('5', 1.0)]</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1504,7 +1516,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence?</t>
+          <t>What est l'emplacement of グレンクリー？</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1517,29 +1529,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence? Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t xml:space="preserve">What est l'emplacement of グレンクリー？ Answer: グレンクリー is located in the United States (USA) at the longitude of -81.5 and latitude of </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t xml:space="preserve">Answer: グレンクリー is located in the United States (USA) at the longitude of -81.5 and latitude of </t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.1273610293865204</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.920876681804657</v>
       </c>
       <c r="I23" t="n">
-        <v>-0</v>
+        <v>0.9431975483894348</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('oe', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Ar', 1.0), ('gy', 1.0), ('ll', 1.0), (' and', 1.0), (' B', 1.0), ('ute', 1.0), (',', 1.0), (' Scotland', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' west', 1.0)]</t>
+          <t>[(' グ', 1.0), ('レン', 1.0), ('ク', 1.0), ('リー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' (', 1.0), ('USA', 1.0), (')', 1.0), (' at', 0.3486), (' the', 1.0), (' longitude', 1.0), (' of', 1.0), (' -', 1.0), ('81', 0.5), ('.', 1.0), ('5', 0.7307), (' and', 1.0), (' latitude', 1.0), (' of', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -1552,7 +1564,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence?</t>
+          <t>What est l'emplacement of グレンクリー？</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1565,29 +1577,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence? Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t xml:space="preserve">What est l'emplacement of グレンクリー？ Answer: グレンクリー is located in the United States (USA) at the longitude of -81.5 and latitude of </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t xml:space="preserve">Answer: グレンクリー is located in the United States (USA) at the longitude of -81.5 and latitude of </t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.1273610293865204</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.920876681804657</v>
       </c>
       <c r="I24" t="n">
-        <v>-0</v>
+        <v>0.9431975483894348</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('oe', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Ar', 1.0), ('gy', 1.0), ('ll', 1.0), (' and', 1.0), (' B', 1.0), ('ute', 1.0), (',', 1.0), (' Scotland', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' west', 1.0)]</t>
+          <t>[(' グ', 1.0), ('レン', 1.0), ('ク', 1.0), ('リー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' (', 1.0), ('USA', 1.0), (')', 1.0), (' at', 0.3486), (' the', 1.0), (' longitude', 1.0), (' of', 1.0), (' -', 1.0), ('81', 0.5), ('.', 1.0), ('5', 0.7307), (' and', 1.0), (' latitude', 1.0), (' of', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1600,7 +1612,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence?</t>
+          <t>What est l'emplacement of グレンクリー？</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1613,29 +1625,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence? Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t>What est l'emplacement of グレンクリー？ Answer: グレンクリー is located in the United States (USA) and the time zone America/New_York (UTC-5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t>Answer: グレンクリー is located in the United States (USA) and the time zone America/New_York (UTC-5</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I25" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('oe', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Ar', 1.0), ('gy', 1.0), ('ll', 1.0), (' and', 1.0), (' B', 1.0), ('ute', 1.0), (',', 1.0), (' Scotland', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' west', 1.0)]</t>
+          <t>[(' グ', 1.0), ('レン', 1.0), ('ク', 1.0), ('リー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' (', 1.0), ('USA', 1.0), (')', 1.0), (' and', 0.6514), (' the', 1.0), (' time', 1.0), (' zone', 1.0), (' America', 1.0), ('/New', 1.0), ('_Y', 1.0), ('ork', 1.0), (' (', 1.0), ('UTC', 1.0), ('-', 1.0), ('5', 1.0)]</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1648,7 +1660,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence?</t>
+          <t>What est l'emplacement of グレンクリー？</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1661,29 +1673,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>What is а 地点 of Glence? Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t>What est l'emplacement of グレンクリー？ Answer: グレンクリー is located in the United States (USA) and the time zone America/New_York (UTC-5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Answer: Glencoe is a village in the county of Argyll and Bute, Scotland. It is located on the west</t>
+          <t>Answer: グレンクリー is located in the United States (USA) and the time zone America/New_York (UTC-5</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I26" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('oe', 1.0), (' is', 1.0), (' a', 1.0), (' village', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' Ar', 1.0), ('gy', 1.0), ('ll', 1.0), (' and', 1.0), (' B', 1.0), ('ute', 1.0), (',', 1.0), (' Scotland', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' west', 1.0)]</t>
+          <t>[(' グ', 1.0), ('レン', 1.0), ('ク', 1.0), ('リー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' (', 1.0), ('USA', 1.0), (')', 1.0), (' and', 0.6514), (' the', 1.0), (' time', 1.0), (' zone', 1.0), (' America', 1.0), ('/New', 1.0), ('_Y', 1.0), ('ork', 1.0), (' (', 1.0), ('UTC', 1.0), ('-', 1.0), ('5', 1.0)]</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -1696,7 +1708,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？</t>
+          <t>What è il emplacement della scala?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1709,29 +1721,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？ Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com The scale of a</t>
+          <t>What è il emplacement della scala? Answer: The location of the scale is on the right side of the piano. The scale is a series of notes that are played in</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com The scale of a</t>
+          <t>Answer: The location of the scale is on the right side of the piano. The scale is a series of notes that are played in</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.3486000001430511</v>
+        <v>0.4243220090866089</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9587228894233704</v>
+        <v>0.9662907719612122</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3673651814460754</v>
+        <v>0.5584209561347961</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' question', 1.0), (' What', 1.0), (' �', 1.0), ('�', 1.0), (' die', 1.0), (' Lage', 1.0), (' of', 1.0), (' ス', 1.0), ('ケ', 1.0), ('ール', 1.0), ('？', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), (' The', 0.3486), (' scale', 1.0), (' of', 1.0), (' a', 1.0)]</t>
+          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' the', 1.0), (' scale', 1.0), (' is', 1.0), (' on', 0.6514), (' the', 1.0), (' right', 0.6514), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' piano', 1.0), ('.', 1.0), (' The', 1.0), (' scale', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0), (' of', 1.0), (' notes', 1.0), (' that', 1.0), (' are', 1.0), (' played', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1744,7 +1756,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？</t>
+          <t>What è il emplacement della scala?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1757,29 +1769,31 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？ Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>What è il emplacement della scala? Answer: The location of the scale is in the right hand corner of the picture.
+What è il emplacement della scala? Answer:</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>Answer: The location of the scale is in the right hand corner of the picture.
+What è il emplacement della scala? Answer:</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.007033751346170902</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9830008745193481</v>
+        <v>0.8201390504837036</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2792104780673981</v>
+        <v>1.679446816444397</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' question', 1.0), (' What', 1.0), (' �', 1.0), ('�', 1.0), (' die', 1.0), (' Lage', 1.0), (' of', 1.0), (' ス', 1.0), ('ケ', 1.0), ('ール', 1.0), ('？', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), ('.', 0.6514), (' The', 1.0), (' scale', 1.0), (' of', 1.0)]</t>
+          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' the', 1.0), (' scale', 1.0), (' is', 1.0), (' in', 0.3486), (' the', 1.0), (' right', 0.1821), (' hand', 0.6357), (' corner', 1.0), (' of', 1.0), (' the', 1.0), (' picture', 0.3486), ('.\n', 0.5), ('What', 1.0), (' è', 1.0), (' il', 1.0), (' em', 1.0), ('placement', 1.0), (' della', 1.0), (' scala', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -1792,7 +1806,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？</t>
+          <t>What è il emplacement della scala?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1805,29 +1819,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？ Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>What è il emplacement della scala? Answer: The location of the scale is on the right side of the piano. The scale is a series of notes that are played in</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>Answer: The location of the scale is on the right side of the piano. The scale is a series of notes that are played in</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.4243220090866089</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9830008745193481</v>
+        <v>0.9662907719612122</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2792104780673981</v>
+        <v>0.5584209561347961</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' question', 1.0), (' What', 1.0), (' �', 1.0), ('�', 1.0), (' die', 1.0), (' Lage', 1.0), (' of', 1.0), (' ス', 1.0), ('ケ', 1.0), ('ール', 1.0), ('？', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), ('.', 0.6514), (' The', 1.0), (' scale', 1.0), (' of', 1.0)]</t>
+          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' the', 1.0), (' scale', 1.0), (' is', 1.0), (' on', 0.6514), (' the', 1.0), (' right', 0.6514), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' piano', 1.0), ('.', 1.0), (' The', 1.0), (' scale', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0), (' of', 1.0), (' notes', 1.0), (' that', 1.0), (' are', 1.0), (' played', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -1840,7 +1854,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？</t>
+          <t>What è il emplacement della scala?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1853,29 +1867,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？ Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>What è il emplacement della scala? Answer: The location of the scale is in the right hand corner of the image. The scale is a small, black, rectangular object</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>Answer: The location of the scale is in the right hand corner of the image. The scale is a small, black, rectangular object</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.006571692414581776</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9830008745193481</v>
+        <v>0.8179129362106323</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2792104780673981</v>
+        <v>1.937865734100342</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' question', 1.0), (' What', 1.0), (' �', 1.0), ('�', 1.0), (' die', 1.0), (' Lage', 1.0), (' of', 1.0), (' ス', 1.0), ('ケ', 1.0), ('ール', 1.0), ('？', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), ('.', 0.6514), (' The', 1.0), (' scale', 1.0), (' of', 1.0)]</t>
+          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' the', 1.0), (' scale', 1.0), (' is', 1.0), (' in', 0.3486), (' the', 1.0), (' right', 0.1821), (' hand', 0.6357), (' corner', 1.0), (' of', 1.0), (' the', 1.0), (' image', 0.6514), ('.', 1.0), (' The', 1.0), (' scale', 1.0), (' is', 1.0), (' a', 0.5), (' small', 1.0), (',', 1.0), (' black', 1.0), (',', 1.0), (' rectangular', 1.0), (' object', 0.5)]</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -1888,7 +1902,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？</t>
+          <t>What è il emplacement della scala?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1901,29 +1915,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>What È die Lage of スケール？ Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>What è il emplacement della scala? Answer: The location of the scale is on the left side of the piano. The scale is a series of notes that are played in</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Answer: 1 question What È die Lage of スケール？ - the answers to estudyassistant.com. The scale of</t>
+          <t>Answer: The location of the scale is on the left side of the piano. The scale is a series of notes that are played in</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9830008745193481</v>
+        <v>0.9424254298210144</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2792104780673981</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 1.0), (' question', 1.0), (' What', 1.0), (' �', 1.0), ('�', 1.0), (' die', 1.0), (' Lage', 1.0), (' of', 1.0), (' ス', 1.0), ('ケ', 1.0), ('ール', 1.0), ('？', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), ('.', 0.6514), (' The', 1.0), (' scale', 1.0), (' of', 1.0)]</t>
+          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' the', 1.0), (' scale', 1.0), (' is', 1.0), (' on', 0.6514), (' the', 1.0), (' left', 0.3486), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' piano', 1.0), ('.', 1.0), (' The', 1.0), (' scale', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0), (' of', 1.0), (' notes', 1.0), (' that', 1.0), (' are', 1.0), (' played', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -1936,7 +1950,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar?</t>
+          <t>什么 is the Standort von Wismar?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1949,29 +1963,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar? Answer: Wismar is a city in the north of Germany. It is located in the state of Mecklenburg-Vorp</t>
+          <t>什么 is the Standort von Wismar? Answer: Wismar is a city in Mecklenburg-Vorpommern, Germany. It is located on the Baltic Sea</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Answer: Wismar is a city in the north of Germany</t>
+          <t>Answer: Wismar is a city in Mecklenburg-Vorpommern, Germany</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.9164904952049255</v>
       </c>
       <c r="I32" t="n">
-        <v>-0</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 0.6514), (' city', 1.0), (' in', 1.0), (' Me', 0.3486), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -1984,7 +1998,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar?</t>
+          <t>什么 is the Standort von Wismar?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1997,29 +2011,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar? Answer: Wismar is a city in the north of Germany. It is located in the state of Mecklenburg-Vorp</t>
+          <t>什么 is the Standort von Wismar? Answer: Wismar is a city in Mecklenburg-Vorpommern, Germany. It is located on the Baltic Sea</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Answer: Wismar is a city in the north of Germany</t>
+          <t>Answer: Wismar is a city in Mecklenburg-Vorpommern, Germany</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.9164904952049255</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 0.6514), (' city', 1.0), (' in', 1.0), (' Me', 0.3486), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -2032,7 +2046,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar?</t>
+          <t>什么 is the Standort von Wismar?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2045,7 +2059,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar? Answer: Wismar is a city in the north of Germany. It is located in the state of Mecklenburg-Vorp</t>
+          <t>什么 is the Standort von Wismar? Answer: Wismar is a city in the north of Germany, in the state of Mecklenburg-Vorpommern.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2054,20 +2068,20 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.4243220090866089</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.9250264167785645</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>0.5584209561347961</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 0.6514), (' city', 1.0), (' in', 1.0), (' the', 0.6514), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2080,7 +2094,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar?</t>
+          <t>什么 is the Standort von Wismar?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2093,29 +2107,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar? Answer: Wismar is a city in the north of Germany. It is located in the state of Mecklenburg-Vorp</t>
+          <t>什么 is the Standort von Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. It</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Answer: Wismar is a city in the north of Germany</t>
+          <t>Answer: Wismar is located in the north of Germany</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.07763321697711945</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.7744702696800232</v>
       </c>
       <c r="I35" t="n">
-        <v>-0</v>
+        <v>0.7018449306488037</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 0.3486), (' in', 1.0), (' the', 1.0), (' north', 0.2227), (' of', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2128,7 +2142,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar?</t>
+          <t>什么 is the Standort von Wismar?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2141,29 +2155,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>What 是 die Lage of Wismar? Answer: Wismar is a city in the north of Germany. It is located in the state of Mecklenburg-Vorp</t>
+          <t>什么 is the Standort von Wismar? Answer: Wismar is a city in Mecklenburg-Vorpommern, Germany. It is located on the Baltic Sea</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Answer: Wismar is a city in the north of Germany</t>
+          <t>Answer: Wismar is a city in Mecklenburg-Vorpommern, Germany</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0.9164904952049255</v>
       </c>
       <c r="I36" t="n">
-        <v>-0</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' a', 0.6514), (' city', 1.0), (' in', 1.0), (' Me', 0.3486), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (',', 1.0), (' Germany', 1.0)]</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -2176,7 +2190,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba?</t>
+          <t>Что такое 这 location of 南巴车站？</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2189,33 +2203,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba? Answer: It is located in the heart of Osaka, Japan. It is a very busy place, and it is a very popular place</t>
+          <t>Что такое 这 location of 南巴车站？ Answer: 南巴车站 is located in the city of 南巴车站. It is located in the province of 南巴车</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Answer: It is located in the heart of Osaka, Japan</t>
+          <t>Answer: 南巴车站 is located in the city of 南巴车站. It is located in the province of 南巴车</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0.06153061613440514</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0.8944656252861023</v>
       </c>
       <c r="I37" t="n">
-        <v>-0</v>
+        <v>1.209765195846558</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' 南', 0.3486), ('巴', 1.0), ('车', 1.0), ('站', 1.0), (' is', 1.0), (' located', 0.7773), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 0.3486), ('站', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.6514), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 1.0)]</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2224,7 +2238,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba?</t>
+          <t>Что такое 这 location of 南巴车站？</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2237,33 +2251,33 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba? Answer: It is located in the heart of Osaka, Japan. It is the largest station in the city and is the main hub for</t>
+          <t xml:space="preserve">Что такое 这 location of 南巴车站？ Answer: The location of 南巴车站 is: 1. 2. 3. 4. 5. </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Answer: It is located in the heart of Osaka, Japan</t>
+          <t xml:space="preserve">Answer: The location of 南巴车站 is: 1. 2. 3. 4. 5. </t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0.0505702793598175</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0.8874743580818176</v>
       </c>
       <c r="I38" t="n">
-        <v>-0</v>
+        <v>0.9810554385185242</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' The', 0.6514), (' location', 1.0), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 1.0), ('站', 1.0), (' is', 1.0), (':', 0.2227), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 0.3486), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2272,7 +2286,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba?</t>
+          <t>Что такое 这 location of 南巴车站？</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2285,33 +2299,33 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba? Answer: It is located in the heart of Osaka, Japan. It is the main station of the city and is the hub of the</t>
+          <t>Что такое 这 location of 南巴车站？ Answer: The location of 南巴车站 is 1.5 km from the center of 南巴车站, 1.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Answer: It is located in the heart of Osaka, Japan</t>
+          <t>Answer: The location of 南巴车站 is 1.5 km from the center of 南巴车站, 1.</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.3298254907131195</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0.9566022157669067</v>
       </c>
       <c r="I39" t="n">
-        <v>-0</v>
+        <v>0.7542452812194824</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' The', 0.6514), (' location', 1.0), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 1.0), ('站', 1.0), (' is', 1.0), (' ', 0.7773), ('1', 1.0), ('.', 1.0), ('5', 1.0), (' km', 1.0), (' from', 1.0), (' the', 1.0), (' center', 0.6514), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 1.0), ('站', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2320,7 +2334,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba?</t>
+          <t>Что такое 这 location of 南巴车站？</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2333,33 +2347,33 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba? Answer: It is located in the heart of Osaka, Japan. It is a very busy place. It is a very busy place.</t>
+          <t xml:space="preserve">Что такое 这 location of 南巴车站？ Answer: The location of 南巴车站 is: 1. 2. 3. 4. 5. </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Answer: It is located in the heart of Osaka, Japan</t>
+          <t xml:space="preserve">Answer: The location of 南巴车站 is: 1. 2. 3. 4. 5. </t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.0505702793598175</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0.8874743580818176</v>
       </c>
       <c r="I40" t="n">
-        <v>-0</v>
+        <v>0.9810554385185242</v>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' The', 0.6514), (' location', 1.0), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 1.0), ('站', 1.0), (' is', 1.0), (':', 0.2227), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 0.3486), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2368,7 +2382,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba?</t>
+          <t>Что такое 这 location of 南巴车站？</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2381,33 +2395,33 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>是什么 the ubicación of Station Namba? Answer: It is located in the heart of Osaka, Japan. It is a very busy station, with many people coming and going.</t>
+          <t xml:space="preserve">Что такое 这 location of 南巴车站？ Answer: The location of 南巴车站 is: 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Answer: It is located in the heart of Osaka, Japan</t>
+          <t xml:space="preserve">Answer: The location of 南巴车站 is: 1. 1. 1. 1. 1. </t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0.09449651092290878</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0.9099481105804443</v>
       </c>
       <c r="I41" t="n">
-        <v>-0</v>
+        <v>0.8929007053375244</v>
       </c>
       <c r="J41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' The', 0.6514), (' location', 1.0), (' of', 1.0), (' 南', 1.0), ('巴', 1.0), ('车', 1.0), ('站', 1.0), (' is', 1.0), (':', 0.2227), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 0.6514), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2416,7 +2430,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal?</t>
+          <t>何 は the location of 2010 ベルギー連邦 election?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2429,12 +2443,13 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal? Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>何 は the location of 2010 ベルギー連邦 election? Answer: 2010 ベルギー連邦 election was held in Belgium.
+What is the location of 2010 ベル</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>Answer: 2010 ベルギー連邦 election was held in Belgium</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2447,15 +2462,15 @@
         <v>-0</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' ', 1.0), ('201', 1.0)]</t>
+          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' ベ', 1.0), ('ル', 1.0), ('ギ', 1.0), ('ー', 1.0), ('連', 1.0), ('邦', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2464,7 +2479,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal?</t>
+          <t>何 は the location of 2010 ベルギー連邦 election?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2477,12 +2492,13 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal? Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>何 は the location of 2010 ベルギー連邦 election? Answer: 2010 ベルギー連邦 election was held in Belgium.
+What is the location of 2010 ベル</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>Answer: 2010 ベルギー連邦 election was held in Belgium</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2495,15 +2511,15 @@
         <v>-0</v>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' ', 1.0), ('201', 1.0)]</t>
+          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' ベ', 1.0), ('ル', 1.0), ('ギ', 1.0), ('ー', 1.0), ('連', 1.0), ('邦', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2512,7 +2528,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal?</t>
+          <t>何 は the location of 2010 ベルギー連邦 election?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2525,12 +2541,13 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal? Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>何 は the location of 2010 ベルギー連邦 election? Answer: 2010 ベルギー連邦 election was held in Belgium.
+What is the location of 2010 ベル</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>Answer: 2010 ベルギー連邦 election was held in Belgium</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2543,15 +2560,15 @@
         <v>-0</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' ', 1.0), ('201', 1.0)]</t>
+          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' ベ', 1.0), ('ル', 1.0), ('ギ', 1.0), ('ー', 1.0), ('連', 1.0), ('邦', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2560,7 +2577,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal?</t>
+          <t>何 は the location of 2010 ベルギー連邦 election?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2573,12 +2590,13 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal? Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>何 は the location of 2010 ベルギー連邦 election? Answer: 2010 ベルギー連邦 election was held in Belgium.
+What is the location of 2010 ベル</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>Answer: 2010 ベルギー連邦 election was held in Belgium</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2591,15 +2609,15 @@
         <v>-0</v>
       </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' ', 1.0), ('201', 1.0)]</t>
+          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' ベ', 1.0), ('ル', 1.0), ('ギ', 1.0), ('ー', 1.0), ('連', 1.0), ('邦', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2608,7 +2626,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal?</t>
+          <t>何 は the location of 2010 ベルギー連邦 election?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2621,12 +2639,13 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>What является the ubicación de 2010 Belgian elección federal? Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>何 は the location of 2010 ベルギー連邦 election? Answer: 2010 ベルギー連邦 election was held in Belgium.
+What is the location of 2010 ベル</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian elección federal What is the ubicación of 2010 Belgian elección federal? Answer: 201</t>
+          <t>Answer: 2010 ベルギー連邦 election was held in Belgium</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2639,15 +2658,15 @@
         <v>-0</v>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' ele', 1.0), ('cción', 1.0), (' federal', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' ', 1.0), ('201', 1.0)]</t>
+          <t>[(' ', 1.0), ('201', 1.0), ('0', 1.0), (' ベ', 1.0), ('ル', 1.0), ('ギ', 1.0), ('ー', 1.0), ('連', 1.0), ('邦', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2656,7 +2675,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ?</t>
+          <t>Cosa è la posizione of CFMJ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2669,31 +2688,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ? Answer: 2 question What является the ubicación из CFMJ? - the answers to estudyassistant.com
-CFMJ is a</t>
+          <t>Cosa è la posizione of CFMJ? Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Answer: 2 question What является the ubicación из CFMJ? - the answers to estudyassistant.com
-CFMJ is a</t>
+          <t>Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9460576772689819</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('2', 0.5), (' question', 1.0), (' What', 1.0), (' является', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' из', 1.0), (' CF', 1.0), ('MJ', 1.0), ('?', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), ('\n', 1.0), ('CF', 0.5), ('MJ', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' non', 1.0), ('-part', 1.0), ('isan', 1.0), (',', 1.0), (' non', 1.0), ('-profit', 1.0), (' organization', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0), (' not', 1.0), (' affiliated', 1.0), (' with', 1.0), (' any', 1.0), (' political', 1.0), (' party', 1.0), (' or', 1.0), (' candidate', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0)]</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -2706,7 +2723,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ?</t>
+          <t>Cosa è la posizione of CFMJ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2719,31 +2736,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ? Answer: 2 question What является the ubicación из CFMJ? - the answers to estudyassistant.com
-What is the location</t>
+          <t>Cosa è la posizione of CFMJ? Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Answer: 2 question What является the ubicación из CFMJ? - the answers to estudyassistant.com
-What is the location</t>
+          <t>Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9460576772689819</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('2', 0.5), (' question', 1.0), (' What', 1.0), (' является', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' из', 1.0), (' CF', 1.0), ('MJ', 1.0), ('?', 1.0), (' -', 1.0), (' the', 1.0), (' answers', 1.0), (' to', 1.0), (' est', 1.0), ('udy', 1.0), ('assistant', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 0.5), (' is', 1.0), (' the', 1.0), (' location', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' non', 1.0), ('-part', 1.0), ('isan', 1.0), (',', 1.0), (' non', 1.0), ('-profit', 1.0), (' organization', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0), (' not', 1.0), (' affiliated', 1.0), (' with', 1.0), (' any', 1.0), (' political', 1.0), (' party', 1.0), (' or', 1.0), (' candidate', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0)]</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -2756,7 +2771,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ?</t>
+          <t>Cosa è la posizione of CFMJ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2769,29 +2784,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ? Answer: 1 Q: What is the location of CFMJ? A: CFMJ is located in Toronto, Ontario. Q:</t>
+          <t>Cosa è la posizione of CFMJ? Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Answer: 1 Q: What is the location of CFMJ? A: CFMJ is located in Toronto, Ontario. Q:</t>
+          <t>Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9460576772689819</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 0.5), (' Q', 1.0), (':', 1.0), (' What', 1.0), (' is', 0.5), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' CF', 1.0), ('MJ', 1.0), ('?', 1.0), (' A', 1.0), (':', 1.0), (' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' Q', 1.0), (':', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' non', 1.0), ('-part', 1.0), ('isan', 1.0), (',', 1.0), (' non', 1.0), ('-profit', 1.0), (' organization', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0), (' not', 1.0), (' affiliated', 1.0), (' with', 1.0), (' any', 1.0), (' political', 1.0), (' party', 1.0), (' or', 1.0), (' candidate', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0)]</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -2804,7 +2819,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ?</t>
+          <t>Cosa è la posizione of CFMJ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2817,29 +2832,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ? Answer: 1 Q: What является the location из CFMJ? A: CFMJ is located in Toronto, Ontario. Q:</t>
+          <t>Cosa è la posizione of CFMJ? Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Answer: 1 Q: What является the location из CFMJ? A: CFMJ is located in Toronto, Ontario. Q:</t>
+          <t>Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.08715000003576279</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.907007098197937</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1.06051230430603</v>
+        <v>-0</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 0.5), (' Q', 1.0), (':', 1.0), (' What', 1.0), (' является', 0.5), (' the', 1.0), (' location', 1.0), (' из', 1.0), (' CF', 1.0), ('MJ', 1.0), ('?', 1.0), (' A', 0.3486), (':', 1.0), (' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' Q', 1.0), (':', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' non', 1.0), ('-part', 1.0), ('isan', 1.0), (',', 1.0), (' non', 1.0), ('-profit', 1.0), (' organization', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0), (' not', 1.0), (' affiliated', 1.0), (' with', 1.0), (' any', 1.0), (' political', 1.0), (' party', 1.0), (' or', 1.0), (' candidate', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0)]</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -2852,7 +2867,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ?</t>
+          <t>Cosa è la posizione of CFMJ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2865,29 +2880,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>What является the ubicación из CFMJ? Answer: 1 Q: What is the location of CFMJ? A: CFMJ is located in Toronto, Ontario. Q:</t>
+          <t>Cosa è la posizione of CFMJ? Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Answer: 1 Q: What is the location of CFMJ? A: CFMJ is located in Toronto, Ontario. Q:</t>
+          <t>Answer: CFMJ is a non-partisan, non-profit organization. We are not affiliated with any political party or candidate. We are</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9460576772689819</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('1', 0.5), (' Q', 1.0), (':', 1.0), (' What', 1.0), (' is', 0.5), (' the', 1.0), (' location', 1.0), (' of', 1.0), (' CF', 1.0), ('MJ', 1.0), ('?', 1.0), (' A', 1.0), (':', 1.0), (' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), ('.', 1.0), (' Q', 1.0), (':', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' a', 1.0), (' non', 1.0), ('-part', 1.0), ('isan', 1.0), (',', 1.0), (' non', 1.0), ('-profit', 1.0), (' organization', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0), (' not', 1.0), (' affiliated', 1.0), (' with', 1.0), (' any', 1.0), (' political', 1.0), (' party', 1.0), (' or', 1.0), (' candidate', 1.0), ('.', 1.0), (' We', 1.0), (' are', 1.0)]</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -2900,7 +2915,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art?</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2913,33 +2928,33 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art? Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？ Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland. It is located in the center of the</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.9362578392028809</v>
       </c>
       <c r="I52" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' 阿', 1.0), ('莫', 1.0), ('斯', 1.0), ('·', 1.0), ('安', 1.0), ('德', 1.0), ('森', 1.0), (' Mus', 1.0), ('ée', 1.0), (' d', 1.0), ("'", 1.0), ('art', 1.0), (' is', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' rue', 1.0), (' de', 1.0), (' la', 1.0), (' Ré', 1.0), ('pub', 1.0)]</t>
+          <t>[(' The', 1.0), (' Am', 0.3486), ('os', 1.0), (' Anderson', 1.0), (' 美', 1.0), ('術', 1.0), (' 博', 1.0), ('物', 1.0), ('館', 1.0), (' is', 1.0), (' a', 1.0), (' museum', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2948,7 +2963,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art?</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2961,33 +2976,33 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art? Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？ Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland. It is located in the center of the</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.9362578392028809</v>
       </c>
       <c r="I53" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' 阿', 1.0), ('莫', 1.0), ('斯', 1.0), ('·', 1.0), ('安', 1.0), ('德', 1.0), ('森', 1.0), (' Mus', 1.0), ('ée', 1.0), (' d', 1.0), ("'", 1.0), ('art', 1.0), (' is', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' rue', 1.0), (' de', 1.0), (' la', 1.0), (' Ré', 1.0), ('pub', 1.0)]</t>
+          <t>[(' The', 1.0), (' Am', 0.3486), ('os', 1.0), (' Anderson', 1.0), (' 美', 1.0), ('術', 1.0), (' 博', 1.0), ('物', 1.0), ('館', 1.0), (' is', 1.0), (' a', 1.0), (' museum', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2996,7 +3011,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art?</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3009,33 +3024,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art? Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？ Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland. It is located in the city center,</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0.9362578392028809</v>
       </c>
       <c r="I54" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' 阿', 1.0), ('莫', 1.0), ('斯', 1.0), ('·', 1.0), ('安', 1.0), ('德', 1.0), ('森', 1.0), (' Mus', 1.0), ('ée', 1.0), (' d', 1.0), ("'", 1.0), ('art', 1.0), (' is', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' rue', 1.0), (' de', 1.0), (' la', 1.0), (' Ré', 1.0), ('pub', 1.0)]</t>
+          <t>[(' The', 1.0), (' Am', 0.3486), ('os', 1.0), (' Anderson', 1.0), (' 美', 1.0), ('術', 1.0), (' 博', 1.0), ('物', 1.0), ('館', 1.0), (' is', 1.0), (' a', 1.0), (' museum', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3044,7 +3059,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art?</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3057,33 +3072,33 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art? Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？ Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland. It is located in the city center,</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>Answer: The Amos Anderson 美術 博物館 is a museum in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0.9362578392028809</v>
       </c>
       <c r="I55" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' 阿', 1.0), ('莫', 1.0), ('斯', 1.0), ('·', 1.0), ('安', 1.0), ('德', 1.0), ('森', 1.0), (' Mus', 1.0), ('ée', 1.0), (' d', 1.0), ("'", 1.0), ('art', 1.0), (' is', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' rue', 1.0), (' de', 1.0), (' la', 1.0), (' Ré', 1.0), ('pub', 1.0)]</t>
+          <t>[(' The', 1.0), (' Am', 0.3486), ('os', 1.0), (' Anderson', 1.0), (' 美', 1.0), ('術', 1.0), (' 博', 1.0), ('物', 1.0), ('館', 1.0), (' is', 1.0), (' a', 1.0), (' museum', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3092,7 +3107,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art?</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3105,33 +3120,33 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>What Ist the location of 阿莫斯·安德森 Musée d'art? Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>What is the 位置 Amos Anderson 美術 博物館？ Answer: The 位置 Amos Anderson 美術 博物館 is a museum in Helsinki, Finland. It is located at the address</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Answer: The location of 阿莫斯·安德森 Musée d'art is: 1, rue de la Répub</t>
+          <t>Answer: The 位置 Amos Anderson 美術 博物館 is a museum in Helsinki, Finland</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.9764684438705444</v>
       </c>
       <c r="I56" t="n">
-        <v>-0</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' location', 1.0), (' of', 1.0), (' 阿', 1.0), ('莫', 1.0), ('斯', 1.0), ('·', 1.0), ('安', 1.0), ('德', 1.0), ('森', 1.0), (' Mus', 1.0), ('ée', 1.0), (' d', 1.0), ("'", 1.0), ('art', 1.0), (' is', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (',', 1.0), (' rue', 1.0), (' de', 1.0), (' la', 1.0), (' Ré', 1.0), ('pub', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 0.6514), ('位置', 1.0), (' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' 美', 1.0), ('術', 1.0), (' 博', 1.0), ('物', 1.0), ('館', 1.0), (' is', 1.0), (' a', 1.0), (' museum', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3140,7 +3155,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What è il posizione of Zelenchuk?</t>
+          <t>Что È the location Di Zelenchuk?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3153,29 +3168,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">What è il posizione of Zelenchuk? Answer: Zelenchuk is located in Russia and his geographical coordinates are 43° 47' 0" North, </t>
+          <t>Что È the location Di Zelenchuk? Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia. It is located on the Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Answer: Zelenchuk is located in Russia and his geographical coordinates are 43° 47' 0" North</t>
+          <t>Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.1521500200033188</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9006803035736084</v>
+        <v>0.9764684438705444</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7086118459701538</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 1.0), (' and', 1.0), (' his', 0.5), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('43', 1.0), ('°', 1.0), (' ', 1.0), ('47', 0.3043)]</t>
+          <t>[(' Z', 0.6514), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ay', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), (' Republic', 1.0), (',', 1.0), (' Russia', 1.0)]</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -3188,7 +3203,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What è il posizione of Zelenchuk?</t>
+          <t>Что È the location Di Zelenchuk?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3201,29 +3216,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">What è il posizione of Zelenchuk? Answer: Zelenchuk is located in Russia and its geographical coordinates are 43° 45' 0" North, </t>
+          <t>Что È the location Di Zelenchuk? Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia. It is located on the Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Answer: Zelenchuk is located in Russia and its geographical coordinates are 43° 45' 0" North</t>
+          <t>Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.06675000488758087</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8603828549385071</v>
+        <v>0.9764684438705444</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6153963804244995</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 1.0), (' and', 1.0), (' its', 0.5), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('43', 1.0), ('°', 1.0), (' ', 1.0), ('45', 0.1335)]</t>
+          <t>[(' Z', 0.6514), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ay', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), (' Republic', 1.0), (',', 1.0), (' Russia', 1.0)]</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -3236,7 +3251,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What è il posizione of Zelenchuk?</t>
+          <t>Что È the location Di Zelenchuk?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3249,29 +3264,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">What è il posizione of Zelenchuk? Answer: Zelenchuk is located in Russia and his geographical coordinates are 43° 47' 0" North, </t>
+          <t>Что È the location Di Zelenchuk? Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia. It is located on the Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Answer: Zelenchuk is located in Russia and his geographical coordinates are 43° 47' 0" North</t>
+          <t>Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.1521500200033188</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9006803035736084</v>
+        <v>0.9764684438705444</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7086118459701538</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 1.0), (' and', 1.0), (' his', 0.5), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('43', 1.0), ('°', 1.0), (' ', 1.0), ('47', 0.3043)]</t>
+          <t>[(' Z', 0.6514), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ay', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), (' Republic', 1.0), (',', 1.0), (' Russia', 1.0)]</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -3284,7 +3299,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What è il posizione of Zelenchuk?</t>
+          <t>Что È the location Di Zelenchuk?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3297,29 +3312,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">What è il posizione of Zelenchuk? Answer: Zelenchuk is located in Russia and its geographical coordinates are 43° 47' 0" North, </t>
+          <t>Что È the location Di Zelenchuk? Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia. It is located on the Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Answer: Zelenchuk is located in Russia and its geographical coordinates are 43° 47' 0" North</t>
+          <t>Answer: Zelenchuk is a city in the Karachay-Cherkess Republic, Russia</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.06675000488758087</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8603828549385071</v>
+        <v>0.9764684438705444</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6153963804244995</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 1.0), (' and', 1.0), (' its', 0.5), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('43', 1.0), ('°', 1.0), (' ', 1.0), ('47', 0.1335)]</t>
+          <t>[(' Z', 0.6514), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ay', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), (' Republic', 1.0), (',', 1.0), (' Russia', 1.0)]</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -3332,7 +3347,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What è il posizione of Zelenchuk?</t>
+          <t>Что È the location Di Zelenchuk?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3345,29 +3360,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">What è il posizione of Zelenchuk? Answer: Zelenchuk is located in Russia and his geographical coordinates are 43° 44' 0" North, </t>
+          <t>Что È the location Di Zelenchuk? Answer: The location of Zelenchuk is in the Republic of Karachay-Cherkessia, Russia. The location of</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Answer: Zelenchuk is located in Russia and his geographical coordinates are 43° 44' 0" North</t>
+          <t>Answer: The location of Zelenchuk is in the Republic of Karachay-Cherkessia, Russia</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.04360000416636467</v>
+        <v>0.1743000000715256</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8402643203735352</v>
+        <v>0.9201768636703491</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5593024492263794</v>
+        <v>0.7139387726783752</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[(' Z', 1.0), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Russia', 1.0), (' and', 1.0), (' his', 0.5), (' geographical', 1.0), (' coordinates', 1.0), (' are', 1.0), (' ', 1.0), ('43', 1.0), ('°', 1.0), (' ', 1.0), ('44', 0.0872)]</t>
+          <t>[(' The', 0.3486), (' location', 1.0), (' of', 1.0), (' Z', 1.0), ('elen', 1.0), ('ch', 1.0), ('uk', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' Republic', 0.5), (' of', 1.0), (' Kar', 1.0), ('ach', 1.0), ('ay', 1.0), ('-Ch', 1.0), ('erk', 1.0), ('ess', 1.0), ('ia', 1.0), (',', 1.0), (' Russia', 1.0)]</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -3380,7 +3395,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto?</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3393,33 +3408,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto? Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, in the region of</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？ Answer: It is a city in Italy. What is the latitude and longitude of Место of 圣托 Stefano D'Aveto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, in the region of</t>
+          <t>Answer: It is a city in Italy</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.1743000000715256</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9325065612792969</v>
+        <v>0.8389213085174561</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7139387726783752</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>[(' the', 0.3486), (' location', 1.0), (' Di', 1.0), (' サ', 1.0), ('ント', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Gen', 1.0), ('oa', 1.0), (',', 1.0), (' in', 0.5), (' the', 1.0), (' region', 1.0), (' of', 1.0)]</t>
+          <t>[(' It', 0.3486), (' is', 1.0), (' a', 1.0), (' city', 1.0), (' in', 1.0), (' Italy', 1.0)]</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3428,7 +3443,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto?</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3441,33 +3456,35 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto? Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, Liguria, Italy</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of �</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, Liguria, Italy</t>
+          <t>Answer: Italy</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.1743000000715256</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H63" t="n">
-        <v>0.9325065612792969</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7139387726783752</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>[(' the', 0.3486), (' location', 1.0), (' Di', 1.0), (' サ', 1.0), ('ント', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Gen', 1.0), ('oa', 1.0), (',', 1.0), (' Lig', 0.5), ('uria', 1.0), (',', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' Italy', 0.6514)]</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3476,7 +3493,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto?</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3489,33 +3506,35 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto? Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, Liguria, Italy</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of �</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, Liguria, Italy</t>
+          <t>Answer: Italy</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.1743000000715256</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9325065612792969</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7139387726783752</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>[(' the', 0.3486), (' location', 1.0), (' Di', 1.0), (' サ', 1.0), ('ント', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Gen', 1.0), ('oa', 1.0), (',', 1.0), (' Lig', 0.5), ('uria', 1.0), (',', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' Italy', 0.6514)]</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3524,7 +3543,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto?</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3537,19 +3556,21 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto? Answer: It is a small town in the province of Genoa, Italy. It is located in the Liguria region, in the</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of �</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Answer: It is a small town in the province of Genoa, Italy</t>
+          <t>Answer: Italy</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>0.6514000296592712</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9675660133361816</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="I65" t="n">
         <v>0.2792104780673981</v>
@@ -3559,11 +3580,11 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Gen', 1.0), ('oa', 1.0), (',', 1.0), (' Italy', 1.0)]</t>
+          <t>[(' Italy', 0.6514)]</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3572,7 +3593,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto?</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3585,33 +3606,35 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qu'est-ce que the location Di サント Stefano d'Aveto? Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, in the region of</t>
+          <t>What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of 圣托 Stefano D'Aveto？ Answer: Italy
+What is Место of �</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Answer: the location Di サント Stefano d'Aveto is a town in the province of Genoa, in the region of</t>
+          <t>Answer: Italy</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.1743000000715256</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H66" t="n">
-        <v>0.9325065612792969</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7139387726783752</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>[(' the', 0.3486), (' location', 1.0), (' Di', 1.0), (' サ', 1.0), ('ント', 1.0), (' Stef', 1.0), ('ano', 1.0), (' d', 1.0), ("'", 1.0), ('Av', 1.0), ('eto', 1.0), (' is', 1.0), (' a', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Gen', 1.0), ('oa', 1.0), (',', 1.0), (' in', 0.5), (' the', 1.0), (' region', 1.0), (' of', 1.0)]</t>
+          <t>[(' Italy', 0.6514)]</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -3620,7 +3643,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com?</t>
+          <t>什么 です location sootoday.comの？</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3633,33 +3656,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com? Answer: It's a news site for Sault Ste. Marie, Ontario, Canada. It's a great site for local news,</t>
+          <t>什么 です location sootoday.comの？ Answer: sootoday.com is an online news portal that provides the latest news, sports, lifestyle, entertainment, politics and business headlines</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Answer: It's a news site for Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: sootoday.com is an online news portal that provides the latest news, sports, lifestyle, entertainment, politics and business headlines</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.2764033675193787</v>
+        <v>0.2171116322278976</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9178454279899597</v>
+        <v>0.9407350420951843</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8376314640045166</v>
+        <v>0.6454112529754639</v>
       </c>
       <c r="J67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), ("'s", 0.6514), (' a', 1.0), (' news', 0.6514), (' site', 1.0), (' for', 0.6514), (' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' so', 1.0), ('ot', 1.0), ('oday', 1.0), ('.com', 1.0), (' is', 1.0), (' an', 1.0), (' online', 1.0), (' news', 1.0), (' portal', 1.0), (' that', 1.0), (' provides', 1.0), (' the', 0.6514), (' latest', 1.0), (' news', 1.0), (',', 1.0), (' sports', 0.3333), (',', 1.0), (' lifestyle', 1.0), (',', 1.0), (' entertainment', 1.0), (',', 1.0), (' politics', 1.0), (' and', 1.0), (' business', 1.0), (' headlines', 1.0)]</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3668,7 +3691,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com?</t>
+          <t>什么 です location sootoday.comの？</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3681,33 +3704,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com? Answer: It’s a news site for Sault Ste. Marie, Ontario, Canada. The site is owned by SooToday.com</t>
+          <t>什么 です location sootoday.comの？ Answer: sootoday.com is an online news portal that provides the latest news, information and stories from the Sault Ste. Marie</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Answer: It’s a news site for Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: sootoday.com is an online news portal that provides the latest news, information and stories from the Sault Ste. Marie</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.1135390251874924</v>
+        <v>0.1414265036582947</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8649871945381165</v>
+        <v>0.9247434139251709</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9931492805480957</v>
+        <v>0.9246217608451843</v>
       </c>
       <c r="J68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), ('’s', 0.3486), (' a', 1.0), (' news', 0.5), (' site', 1.0), (' for', 0.6514), (' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' so', 1.0), ('ot', 1.0), ('oday', 1.0), ('.com', 1.0), (' is', 1.0), (' an', 1.0), (' online', 1.0), (' news', 1.0), (' portal', 1.0), (' that', 1.0), (' provides', 1.0), (' the', 0.6514), (' latest', 1.0), (' news', 1.0), (',', 1.0), (' information', 0.3333), (' and', 1.0), (' stories', 1.0), (' from', 1.0), (' the', 0.6514), (' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0)]</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3716,7 +3739,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com?</t>
+          <t>什么 です location sootoday.comの？</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3729,33 +3752,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com? Answer: It's a news site. It's a news site. It's a news site. It's a news site. It</t>
+          <t>什么 です location sootoday.comの？ Answer: sootoday.com is an online news portal that provides the latest news, sports, lifestyle, entertainment, politics and business headlines</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Answer: It's a news site. It's a news site. It's a news site. It's a news site. It</t>
+          <t>Answer: sootoday.com is an online news portal that provides the latest news, sports, lifestyle, entertainment, politics and business headlines</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.09635422378778458</v>
+        <v>0.2171116322278976</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9106569886207581</v>
+        <v>0.9407350420951843</v>
       </c>
       <c r="I69" t="n">
-        <v>1.204996585845947</v>
+        <v>0.6454112529754639</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), ("'s", 0.6514), (' a', 1.0), (' news', 0.6514), (' site', 1.0), ('.', 0.3486), (' It', 1.0), ("'s", 1.0), (' a', 0.6514), (' news', 1.0), (' site', 1.0), ('.', 1.0), (' It', 1.0), ("'s", 1.0), (' a', 1.0), (' news', 1.0), (' site', 1.0), ('.', 1.0), (' It', 1.0), ("'s", 1.0), (' a', 1.0), (' news', 1.0), (' site', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[(' so', 1.0), ('ot', 1.0), ('oday', 1.0), ('.com', 1.0), (' is', 1.0), (' an', 1.0), (' online', 1.0), (' news', 1.0), (' portal', 1.0), (' that', 1.0), (' provides', 1.0), (' the', 0.6514), (' latest', 1.0), (' news', 1.0), (',', 1.0), (' sports', 0.3333), (',', 1.0), (' lifestyle', 1.0), (',', 1.0), (' entertainment', 1.0), (',', 1.0), (' politics', 1.0), (' and', 1.0), (' business', 1.0), (' headlines', 1.0)]</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3764,7 +3787,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com?</t>
+          <t>什么 です location sootoday.comの？</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3777,33 +3800,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com? Answer: It’s a website that is owned by the SooToday.com company. It’s a website that is owned by the So</t>
+          <t>什么 です location sootoday.comの？ Answer: sootoday.com is an online news portal that provides the latest news, information and stories from around the world. It is</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Answer: It’s a website that is owned by the SooToday.com company. It’s a website that is owned by the So</t>
+          <t>Answer: sootoday.com is an online news portal that provides the latest news, information and stories from around the world. It is</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.04722951352596283</v>
+        <v>0.07568510621786118</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8850514888763428</v>
+        <v>0.9019042253494263</v>
       </c>
       <c r="I70" t="n">
-        <v>1.277128219604492</v>
+        <v>1.012776494026184</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), ('’s', 0.3486), (' a', 1.0), (' website', 0.5), (' that', 1.0), (' is', 1.0), (' owned', 1.0), (' by', 1.0), (' the', 1.0), (' So', 1.0), ('o', 1.0), ('Today', 1.0), ('.com', 1.0), (' company', 0.7773), ('.', 1.0), (' It', 0.3486), ('’s', 1.0), (' a', 1.0), (' website', 1.0), (' that', 1.0), (' is', 1.0), (' owned', 1.0), (' by', 1.0), (' the', 1.0), (' So', 1.0)]</t>
+          <t>[(' so', 1.0), ('ot', 1.0), ('oday', 1.0), ('.com', 1.0), (' is', 1.0), (' an', 1.0), (' online', 1.0), (' news', 1.0), (' portal', 1.0), (' that', 1.0), (' provides', 1.0), (' the', 0.6514), (' latest', 1.0), (' news', 1.0), (',', 1.0), (' information', 0.3333), (' and', 1.0), (' stories', 1.0), (' from', 1.0), (' around', 0.3486), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3812,7 +3835,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com?</t>
+          <t>什么 です location sootoday.comの？</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3825,33 +3848,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>What 是 posizione из SooToday.com? Answer: It's a news site. It's a news site. It's a news site. It's a news site. It</t>
+          <t>什么 です location sootoday.comの？ Answer: sootoday.com is an online news portal that provides the latest news, sports, lifestyle, entertainment, politics and business headlines</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Answer: It's a news site. It's a news site. It's a news site. It's a news site. It</t>
+          <t>Answer: sootoday.com is an online news portal that provides the latest news, sports, lifestyle, entertainment, politics and business headlines</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.09635422378778458</v>
+        <v>0.2171116322278976</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9106569886207581</v>
+        <v>0.9407350420951843</v>
       </c>
       <c r="I71" t="n">
-        <v>1.204996585845947</v>
+        <v>0.6454112529754639</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>[(' It', 1.0), ("'s", 0.6514), (' a', 1.0), (' news', 0.6514), (' site', 1.0), ('.', 0.3486), (' It', 1.0), ("'s", 1.0), (' a', 0.6514), (' news', 1.0), (' site', 1.0), ('.', 1.0), (' It', 1.0), ("'s", 1.0), (' a', 1.0), (' news', 1.0), (' site', 1.0), ('.', 1.0), (' It', 1.0), ("'s", 1.0), (' a', 1.0), (' news', 1.0), (' site', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[(' so', 1.0), ('ot', 1.0), ('oday', 1.0), ('.com', 1.0), (' is', 1.0), (' an', 1.0), (' online', 1.0), (' news', 1.0), (' portal', 1.0), (' that', 1.0), (' provides', 1.0), (' the', 0.6514), (' latest', 1.0), (' news', 1.0), (',', 1.0), (' sports', 0.3333), (',', 1.0), (' lifestyle', 1.0), (',', 1.0), (' entertainment', 1.0), (',', 1.0), (' politics', 1.0), (' and', 1.0), (' business', 1.0), (' headlines', 1.0)]</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3860,7 +3883,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena?</t>
+          <t>什么 is the 地点 of Sena Medaille?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3873,29 +3896,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena? Answer: ¿Medalla Sena? is a Spanish word that means “Medal of Honor”. It is a military decoration awarded to</t>
+          <t>什么 is the 地点 of Sena Medaille? Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at Sena Medaille</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Answer: ¿Medalla Sena? is a Spanish word that means “Medal of Honor”. It is a military decoration awarded to</t>
+          <t>Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at Sena Medaille</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9460576772689819</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[(' ¿', 0.5), ('Med', 1.0), ('alla', 1.0), (' Sen', 1.0), ('a', 1.0), ('?', 1.0), (' is', 1.0), (' a', 1.0), (' Spanish', 1.0), (' word', 1.0), (' that', 1.0), (' means', 1.0), (' “', 1.0), ('Med', 1.0), ('al', 1.0), (' of', 1.0), (' Honor', 1.0), ('”.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' military', 1.0), (' decoration', 1.0), (' awarded', 1.0), (' to', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' the', 1.0), (' 地', 1.0), ('点', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), ('.', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' Sen', 0.5), ('a', 1.0), (' Med', 1.0), ('aille', 1.0)]</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3908,7 +3931,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena?</t>
+          <t>什么 is the 地点 of Sena Medaille?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3921,29 +3944,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena? Answer: ¿Medalla Sena? is a Spanish word that means “Medal of Honor.” It is a military decoration awarded to</t>
+          <t>什么 is the 地点 of Sena Medaille? Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at 1 Sena</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Answer: ¿Medalla Sena? is a Spanish word that means “Medal of Honor.” It is a military decoration awarded to</t>
+          <t>Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at 1 Sena</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9460576772689819</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[(' ¿', 0.5), ('Med', 1.0), ('alla', 1.0), (' Sen', 1.0), ('a', 1.0), ('?', 1.0), (' is', 1.0), (' a', 1.0), (' Spanish', 1.0), (' word', 1.0), (' that', 1.0), (' means', 1.0), (' “', 1.0), ('Med', 1.0), ('al', 1.0), (' of', 1.0), (' Honor', 1.0), ('.”', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' military', 1.0), (' decoration', 1.0), (' awarded', 1.0), (' to', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' the', 1.0), (' 地', 1.0), ('点', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), ('.', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 0.5), ('1', 1.0), (' Sen', 1.0), ('a', 1.0)]</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3956,7 +3979,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena?</t>
+          <t>什么 is the 地点 of Sena Medaille?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3969,29 +3992,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena? Answer: The position of Medalla Sena is 10° 00' 00" N, 74° 00'</t>
+          <t>什么 is the 地点 of Sena Medaille? Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at Sena Medaille</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Answer: The position of Medalla Sena is 10° 00' 00" N, 74° 00'</t>
+          <t>Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at Sena Medaille</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.111349992454052</v>
+        <v>0.5</v>
       </c>
       <c r="H74" t="n">
-        <v>0.9159412384033203</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6810533404350281</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' position', 1.0), (' of', 1.0), (' Med', 1.0), ('alla', 1.0), (' Sen', 1.0), ('a', 1.0), (' is', 1.0), (' ', 1.0), ('10', 1.0), ('°', 1.0), (' ', 1.0), ('00', 0.2227), ("'", 1.0), (' ', 1.0), ('00', 1.0), ('"', 1.0), (' N', 1.0), (',', 1.0), (' ', 1.0), ('74', 1.0), ('°', 1.0), (' ', 1.0), ('00', 1.0), ("'", 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' the', 1.0), (' 地', 1.0), ('点', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), ('.', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' Sen', 0.5), ('a', 1.0), (' Med', 1.0), ('aille', 1.0)]</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -4004,7 +4027,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena?</t>
+          <t>什么 is the 地点 of Sena Medaille?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4017,29 +4040,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena? Answer: The position of Medalla Sena is 10° 0' 0" N, 74° 0'</t>
+          <t>什么 is the 地点 of Sena Medaille? Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at 1 Sena</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Answer: The position of Medalla Sena is 10° 0' 0" N, 74° 0'</t>
+          <t>Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at 1 Sena</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.3886500000953674</v>
+        <v>0.5</v>
       </c>
       <c r="H75" t="n">
-        <v>0.9629025459289551</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' position', 1.0), (' of', 1.0), (' Med', 1.0), ('alla', 1.0), (' Sen', 1.0), ('a', 1.0), (' is', 1.0), (' ', 1.0), ('10', 1.0), ('°', 1.0), (' ', 1.0), ('0', 0.7773), ("'", 1.0), (' ', 1.0), ('0', 1.0), ('"', 1.0), (' N', 1.0), (',', 1.0), (' ', 1.0), ('74', 1.0), ('°', 1.0), (' ', 1.0), ('0', 1.0), ("'", 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' the', 1.0), (' 地', 1.0), ('点', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), ('.', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 0.5), ('1', 1.0), (' Sen', 1.0), ('a', 1.0)]</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -4052,7 +4075,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena?</t>
+          <t>什么 is the 地点 of Sena Medaille?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4065,29 +4088,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>What es la posizione of ¿Medalla Sena? Answer: The position of Medalla Sena is 10° 0' 0" N, 74° 0'</t>
+          <t>什么 is the 地点 of Sena Medaille? Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at Sena Medaille</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Answer: The position of Medalla Sena is 10° 0' 0" N, 74° 0'</t>
+          <t>Answer: Sena Medaille is the 地点 of Sena Medaille. Sena Medaille is located at Sena Medaille</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.3886500000953674</v>
+        <v>0.5</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9629025459289551</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' position', 1.0), (' of', 1.0), (' Med', 1.0), ('alla', 1.0), (' Sen', 1.0), ('a', 1.0), (' is', 1.0), (' ', 1.0), ('10', 1.0), ('°', 1.0), (' ', 1.0), ('0', 0.7773), ("'", 1.0), (' ', 1.0), ('0', 1.0), ('"', 1.0), (' N', 1.0), (',', 1.0), (' ', 1.0), ('74', 1.0), ('°', 1.0), (' ', 1.0), ('0', 1.0), ("'", 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' the', 1.0), (' 地', 1.0), ('点', 1.0), (' of', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), ('.', 1.0), (' Sen', 1.0), ('a', 1.0), (' Med', 1.0), ('aille', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' Sen', 0.5), ('a', 1.0), (' Med', 1.0), ('aille', 1.0)]</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -4100,7 +4123,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？</t>
+          <t>Cosa è the расположение Lake Калирая?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4113,29 +4136,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？ Answer: Lake カリラヤ is located in the north of the island of カリラヤ. It is the largest lake in</t>
+          <t>Cosa è the расположение Lake Калирая? Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Answer: Lake カリラヤ is located in the north of the island of カリラヤ. It is the largest lake in</t>
+          <t>Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H77" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' カ', 1.0), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' カ', 0.7773), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), ('.', 0.6514), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' lake', 1.0), (' in', 1.0)]</t>
+          <t>[(' The', 0.6514), (' рас', 1.0), ('пол', 1.0), ('ож', 1.0), ('ение', 1.0), (' Lake', 1.0), (' К', 1.0), ('али', 1.0), ('ра', 1.0), ('я', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -4148,7 +4171,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？</t>
+          <t>Cosa è the расположение Lake Калирая?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4161,29 +4184,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？ Answer: Lake カリラヤ is located in the north of the island of カリラヤ in the Caribbean Sea. It is</t>
+          <t>Cosa è the расположение Lake Калирая? Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Answer: Lake カリラヤ is located in the north of the island of カリラヤ in the Caribbean Sea. It is</t>
+          <t>Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.2709667682647705</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H78" t="n">
-        <v>0.949110209941864</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5631895065307617</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' カ', 1.0), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' カ', 0.7773), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), (' in', 0.3486), (' the', 1.0), (' Caribbean', 1.0), (' Sea', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' The', 0.6514), (' рас', 1.0), ('пол', 1.0), ('ож', 1.0), ('ение', 1.0), (' Lake', 1.0), (' К', 1.0), ('али', 1.0), ('ра', 1.0), ('я', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -4196,7 +4219,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？</t>
+          <t>Cosa è the расположение Lake Калирая?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4209,29 +4232,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？ Answer: Lake カリラヤ is located in the north of the island of Hokkaido, Japan. It is the largest</t>
+          <t>Cosa è the расположение Lake Калирая? Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Answer: Lake カリラヤ is located in the north of the island of Hokkaido, Japan. It is the largest</t>
+          <t>Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.2226999849081039</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9416918158531189</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3344797492027283</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' カ', 1.0), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' Hok', 0.2227), ('k', 1.0), ('aid', 1.0), ('o', 1.0), (',', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0)]</t>
+          <t>[(' The', 0.6514), (' рас', 1.0), ('пол', 1.0), ('ож', 1.0), ('ение', 1.0), (' Lake', 1.0), (' К', 1.0), ('али', 1.0), ('ра', 1.0), ('я', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -4244,7 +4267,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？</t>
+          <t>Cosa è the расположение Lake Калирая?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4257,29 +4280,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？ Answer: Lake カリラヤ is located in the north of the island of カリラヤ. It is the largest lake in</t>
+          <t>Cosa è the расположение Lake Калирая? Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Answer: Lake カリラヤ is located in the north of the island of カリラヤ. It is the largest lake in</t>
+          <t>Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' カ', 1.0), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' カ', 0.7773), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), ('.', 0.6514), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' lake', 1.0), (' in', 1.0)]</t>
+          <t>[(' The', 0.6514), (' рас', 1.0), ('пол', 1.0), ('ож', 1.0), ('ение', 1.0), (' Lake', 1.0), (' К', 1.0), ('али', 1.0), ('ра', 1.0), ('я', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4292,7 +4315,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？</t>
+          <t>Cosa è the расположение Lake Калирая?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4305,29 +4328,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>What es el расположение of Lake カリラヤ？ Answer: Lake カリラヤ is located in the north of the island of カリラヤ. It is the largest lake in</t>
+          <t>Cosa è the расположение Lake Калирая? Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Answer: Lake カリラヤ is located in the north of the island of カリラヤ. It is the largest lake in</t>
+          <t>Answer: The расположение Lake Калирая is in the state of California, in the United States of America. The</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.5063332319259644</v>
+        <v>0.6514000296592712</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9731447696685791</v>
+        <v>0.9830008745193481</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4750348329544067</v>
+        <v>0.2792104780673981</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' カ', 1.0), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), (' of', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' カ', 0.7773), ('リ', 1.0), ('ラ', 1.0), ('ヤ', 1.0), ('.', 0.6514), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' lake', 1.0), (' in', 1.0)]</t>
+          <t>[(' The', 0.6514), (' рас', 1.0), ('пол', 1.0), ('ож', 1.0), ('ение', 1.0), (' Lake', 1.0), (' К', 1.0), ('али', 1.0), ('ра', 1.0), ('я', 1.0), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4340,7 +4363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho?</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4353,33 +4376,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.3000, 26.1000. What is</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho? Answer: Didymoteicho is located in Greece and the postal code is 68200.
+Qu'est-ce que the posizione of</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.3000, 26.1000. What is</t>
+          <t>Answer: Didymoteicho is located in Greece and the postal code is 68200</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.2057999968528748</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9387237429618835</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3253390192985535</v>
+        <v>-0</v>
       </c>
       <c r="J82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('300', 0.2058), ('0', 1.0), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('100', 1.0), ('0', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0), (' and', 1.0), (' the', 1.0), (' postal', 1.0), (' code', 1.0), (' is', 1.0), (' ', 1.0), ('682', 1.0), ('00', 1.0)]</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4388,7 +4412,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho?</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4401,33 +4425,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.2700, 26.1000. What is</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho? Answer: Didymoteicho is located in Greece and the postal code is 68200.
+Qu'est-ce que the posizione of</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.2700, 26.1000. What is</t>
+          <t>Answer: Didymoteicho is located in Greece and the postal code is 68200</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.0196646973490715</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0.854569673538208</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5331836938858032</v>
+        <v>-0</v>
       </c>
       <c r="J83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('270', 0.059), ('0', 1.0), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('100', 0.3333), ('0', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0), (' and', 1.0), (' the', 1.0), (' postal', 1.0), (' code', 1.0), (' is', 1.0), (' ', 1.0), ('682', 1.0), ('00', 1.0)]</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -4436,7 +4461,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho?</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4449,33 +4474,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.3100, 26.1000. What is</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho? Answer: Didymoteicho is located in Greece and the postal code is 68200.
+Qu'est-ce que the posizione of</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.3100, 26.1000. What is</t>
+          <t>Answer: Didymoteicho is located in Greece and the postal code is 68200</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.04586070403456688</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.884010910987854</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3628072142601013</v>
+        <v>-0</v>
       </c>
       <c r="J84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('310', 0.059), ('0', 1.0), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('100', 0.7773), ('0', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0), (' and', 1.0), (' the', 1.0), (' postal', 1.0), (' code', 1.0), (' is', 1.0), (' ', 1.0), ('682', 1.0), ('00', 1.0)]</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -4484,7 +4510,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho?</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4497,33 +4523,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.3333, 26.1667. What is</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho? Answer: Didymoteicho is located in Greece and the postal code is 68200.
+Qu'est-ce que the posizione of</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.3333, 26.1667. What is</t>
+          <t>Answer: Didymoteicho is located in Greece and the postal code is 68200</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.1308270543813705</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>0.921866238117218</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>0.613329291343689</v>
+        <v>-0</v>
       </c>
       <c r="J85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('333', 0.2058), ('3', 1.0), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('166', 0.6357), ('7', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0), (' and', 1.0), (' the', 1.0), (' postal', 1.0), (' code', 1.0), (' is', 1.0), (' ', 1.0), ('682', 1.0), ('00', 1.0)]</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -4532,7 +4559,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho?</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4545,33 +4572,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Was is the posizione из Didymoteicho? Answer: Didymoteicho is located in the following coordinates: 41.2800, 26.0500. What is</t>
+          <t>Qu'est-ce que the posizione of Didymoteicho? Answer: Didymoteicho is located in Greece and the postal code is 68200.
+Qu'est-ce que the posizione of</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in the following coordinates: 41.2800, 26.0500. What is</t>
+          <t>Answer: Didymoteicho is located in Greece and the postal code is 68200</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.08999635279178619</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.9081738591194153</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6870455145835876</v>
+        <v>-0</v>
       </c>
       <c r="J86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' following', 1.0), (' coordinates', 1.0), (':', 1.0), (' ', 1.0), ('41', 1.0), ('.', 1.0), ('280', 0.2058), ('0', 1.0), (',', 1.0), (' ', 1.0), ('26', 1.0), ('.', 1.0), ('050', 0.4373), ('0', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Greece', 1.0), (' and', 1.0), (' the', 1.0), (' postal', 1.0), (' code', 1.0), (' is', 1.0), (' ', 1.0), ('682', 1.0), ('00', 1.0)]</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4580,7 +4608,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake?</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4593,12 +4621,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake? Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4615,7 +4643,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' O', 1.0), ('cé', 1.0), ('ano', 1.0), (' �', 1.0), ('�', 1.0), ('nd', 1.0), ('ico', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 1.0), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' was', 1.0), (' an', 1.0), (' under', 1.0), ('sea', 1.0), (' meg', 1.0), ('ath', 1.0), ('rust', 1.0), (' earthquake', 1.0), (' that', 1.0), (' occurred', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4628,7 +4656,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake?</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4641,12 +4669,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake? Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -4663,7 +4691,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' O', 1.0), ('cé', 1.0), ('ano', 1.0), (' �', 1.0), ('�', 1.0), ('nd', 1.0), ('ico', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 1.0), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' was', 1.0), (' an', 1.0), (' under', 1.0), ('sea', 1.0), (' meg', 1.0), ('ath', 1.0), ('rust', 1.0), (' earthquake', 1.0), (' that', 1.0), (' occurred', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4676,7 +4704,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake?</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4689,12 +4717,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake? Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4711,7 +4739,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' O', 1.0), ('cé', 1.0), ('ano', 1.0), (' �', 1.0), ('�', 1.0), ('nd', 1.0), ('ico', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 1.0), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' was', 1.0), (' an', 1.0), (' under', 1.0), ('sea', 1.0), (' meg', 1.0), ('ath', 1.0), ('rust', 1.0), (' earthquake', 1.0), (' that', 1.0), (' occurred', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4724,7 +4752,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake?</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4737,12 +4765,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake? Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4759,7 +4787,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' O', 1.0), ('cé', 1.0), ('ano', 1.0), (' �', 1.0), ('�', 1.0), ('nd', 1.0), ('ico', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 1.0), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' was', 1.0), (' an', 1.0), (' under', 1.0), ('sea', 1.0), (' meg', 1.0), ('ath', 1.0), ('rust', 1.0), (' earthquake', 1.0), (' that', 1.0), (' occurred', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -4772,7 +4800,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake?</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4785,12 +4813,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Was является location of 2004 Océano Índico earthquake? Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Qué es la ubicación von 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Océano Índico earthquake occurred on 26 December 2004 at 00:58</t>
+          <t>Answer: The 2004 Indian Ocean earthquake was an undersea megathrust earthquake that occurred at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -4807,7 +4835,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' O', 1.0), ('cé', 1.0), ('ano', 1.0), (' �', 1.0), ('�', 1.0), ('nd', 1.0), ('ico', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 1.0), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' was', 1.0), (' an', 1.0), (' under', 1.0), ('sea', 1.0), (' meg', 1.0), ('ath', 1.0), ('rust', 1.0), (' earthquake', 1.0), (' that', 1.0), (' occurred', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4820,7 +4848,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner?</t>
+          <t>What es the ubicación de フォークナー？</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4833,33 +4861,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner? Answer: Fawkner is a suburb of Melbourne, Victoria, Australia, 11 km north of Melbourne's Central Business District. Its</t>
+          <t>What es the ubicación de フォークナー？ Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is a suburb of Melbourne, Victoria, Australia</t>
+          <t>Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.5063332319259644</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.9731447696685791</v>
       </c>
       <c r="I92" t="n">
-        <v>-0</v>
+        <v>0.4750348329544067</v>
       </c>
       <c r="J92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' suburb', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' フ', 1.0), ('ォ', 1.0), ('ーク', 1.0), ('ナー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (',', 0.6514), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.7773), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4868,7 +4896,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner?</t>
+          <t>What es the ubicación de フォークナー？</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4881,33 +4909,35 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner? Answer: Fawkner is a suburb of Melbourne, Victoria, Australia, 10 km north of Melbourne's Central Business District. Its</t>
+          <t>What es the ubicación de フォークナー？ Answer: フォークナー is located in the United States.
+What es the ubicación de フォークナー？ Answer: フ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is a suburb of Melbourne, Victoria, Australia</t>
+          <t>Answer: フォークナー is located in the United States.
+What es the ubicación de フォークナー？ Answer: フ</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0.9587228894233704</v>
       </c>
       <c r="I93" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' suburb', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' フ', 1.0), ('ォ', 1.0), ('ーク', 1.0), ('ナー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.\n', 0.3486), ('What', 1.0), (' es', 1.0), (' the', 1.0), (' ubic', 1.0), ('ación', 1.0), (' de', 1.0), (' フ', 1.0), ('ォ', 1.0), ('ーク', 1.0), ('ナー', 1.0), ('？', 1.0), (' Answer', 1.0), (':', 1.0), (' フ', 1.0)]</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4916,7 +4946,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner?</t>
+          <t>What es the ubicación de フォークナー？</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4929,33 +4959,33 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner? Answer: Fawkner is a suburb of Melbourne, Victoria, Australia, 10 km north of Melbourne's Central Business District. Its</t>
+          <t>What es the ubicación de フォークナー？ Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is a suburb of Melbourne, Victoria, Australia</t>
+          <t>Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.5063332319259644</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0.9731447696685791</v>
       </c>
       <c r="I94" t="n">
-        <v>-0</v>
+        <v>0.4750348329544067</v>
       </c>
       <c r="J94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' suburb', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' フ', 1.0), ('ォ', 1.0), ('ーク', 1.0), ('ナー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (',', 0.6514), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.7773), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4964,7 +4994,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner?</t>
+          <t>What es the ubicación de フォークナー？</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4977,33 +5007,33 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner? Answer: Fawkner is a suburb of Melbourne, Victoria, Australia, 10 km north of Melbourne's Central Business District. Its</t>
+          <t>What es the ubicación de フォークナー？ Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is a suburb of Melbourne, Victoria, Australia</t>
+          <t>Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.5063332319259644</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0.9731447696685791</v>
       </c>
       <c r="I95" t="n">
-        <v>-0</v>
+        <v>0.4750348329544067</v>
       </c>
       <c r="J95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' suburb', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' フ', 1.0), ('ォ', 1.0), ('ーク', 1.0), ('ナー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (',', 0.6514), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.7773), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5012,7 +5042,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner?</t>
+          <t>What es the ubicación de フォークナー？</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5025,33 +5055,33 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Что です location Di Fawkner? Answer: Fawkner is a suburb of Melbourne, Victoria, Australia, 10 km north of Melbourne's Central Business District. Its</t>
+          <t>What es the ubicación de フォークナー？ Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is a suburb of Melbourne, Victoria, Australia</t>
+          <t>Answer: フォークナー is located in the United States, in the state of New York, in the city of New York.</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.5063332319259644</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0.9731447696685791</v>
       </c>
       <c r="I96" t="n">
-        <v>-0</v>
+        <v>0.4750348329544067</v>
       </c>
       <c r="J96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' a', 1.0), (' suburb', 1.0), (' of', 1.0), (' Melbourne', 1.0), (',', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' フ', 1.0), ('ォ', 1.0), ('ーク', 1.0), ('ナー', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (',', 0.6514), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.7773), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5060,7 +5090,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？</t>
+          <t>何ですか the location の Abu Ghosh?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5073,12 +5103,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？ Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>何ですか the location の Abu Ghosh? Answer: Abu Ghosh is a small town in Israel, located about 10 km west of Jerusalem. It is known for its restaurants</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>Answer: Abu Ghosh is a small town in Israel</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5091,15 +5121,15 @@
         <v>-0</v>
       </c>
       <c r="J97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>[(' 阿', 1.0), ('布', 1.0), ('·', 1.0), ('�', 1.0), ('�', 1.0), ('什', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' 阿', 1.0), ('拉', 1.0), ('巴', 1.0), ('马', 1.0), ('州', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -5108,7 +5138,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？</t>
+          <t>何ですか the location の Abu Ghosh?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5121,12 +5151,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？ Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>何ですか the location の Abu Ghosh? Answer: Abu Ghosh is a small town in Israel, located about 10 kilometers west of Jerusalem. It is known for its ancient</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>Answer: Abu Ghosh is a small town in Israel</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5139,15 +5169,15 @@
         <v>-0</v>
       </c>
       <c r="J98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>[(' 阿', 1.0), ('布', 1.0), ('·', 1.0), ('�', 1.0), ('�', 1.0), ('什', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' 阿', 1.0), ('拉', 1.0), ('巴', 1.0), ('马', 1.0), ('州', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5156,7 +5186,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？</t>
+          <t>何ですか the location の Abu Ghosh?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5169,12 +5199,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？ Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>何ですか the location の Abu Ghosh? Answer: Abu Ghosh is a small town in Israel, located about 10 kilometers west of Jerusalem. It is known for its ancient</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>Answer: Abu Ghosh is a small town in Israel</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5187,15 +5217,15 @@
         <v>-0</v>
       </c>
       <c r="J99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>[(' 阿', 1.0), ('布', 1.0), ('·', 1.0), ('�', 1.0), ('�', 1.0), ('什', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' 阿', 1.0), ('拉', 1.0), ('巴', 1.0), ('马', 1.0), ('州', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -5204,7 +5234,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？</t>
+          <t>何ですか the location の Abu Ghosh?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5217,12 +5247,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？ Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>何ですか the location の Abu Ghosh? Answer: Abu Ghosh is a small town in Israel, located about 10 kilometers west of Jerusalem. It is known for its ancient</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>Answer: Abu Ghosh is a small town in Israel</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -5235,15 +5265,15 @@
         <v>-0</v>
       </c>
       <c r="J100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[(' 阿', 1.0), ('布', 1.0), ('·', 1.0), ('�', 1.0), ('�', 1.0), ('什', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' 阿', 1.0), ('拉', 1.0), ('巴', 1.0), ('马', 1.0), ('州', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -5252,7 +5282,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？</t>
+          <t>何ですか the location の Abu Ghosh?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5265,12 +5295,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Quoi 是 the location of 阿布·戈什？ Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>何ですか the location の Abu Ghosh? Answer: Abu Ghosh is a small town in Israel, located about 10 kilometers west of Jerusalem. It is known for its ancient</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Answer: 阿布·戈什 is located in the state of 阿拉巴马州, United States of America, and the</t>
+          <t>Answer: Abu Ghosh is a small town in Israel</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5283,15 +5313,15 @@
         <v>-0</v>
       </c>
       <c r="J101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>[(' 阿', 1.0), ('布', 1.0), ('·', 1.0), ('�', 1.0), ('�', 1.0), ('什', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' 阿', 1.0), ('拉', 1.0), ('巴', 1.0), ('马', 1.0), ('州', 1.0), (',', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' Israel', 1.0)]</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
